--- a/public/asset/VendorEmailerTemplate.xlsx
+++ b/public/asset/VendorEmailerTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajaz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajaz\Desktop\BulkMailer\bulk_emailer_frontend\public\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9767A1CC-0D34-4762-A2AC-4A08518EBBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4B528C-57C5-4F20-967D-49267C987E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>Email</t>
-  </si>
-  <si>
-    <t>aahamad@neuvays.net</t>
   </si>
 </sst>
 </file>
@@ -386,9 +383,7 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:1" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
